--- a/Minimum Inventory Model.xlsx
+++ b/Minimum Inventory Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZachF\Desktop\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F439593A-3CB1-42BC-BFB3-D9F37C40AE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDAF511-B891-473E-B189-0A49CC78B9F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{4C7A1581-7433-4ABA-BE68-43C5F4B97E1B}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{4C7A1581-7433-4ABA-BE68-43C5F4B97E1B}"/>
   </bookViews>
   <sheets>
     <sheet name="OH" sheetId="3" r:id="rId1"/>
